--- a/public/客戶資料模板.xlsx
+++ b/public/客戶資料模板.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/krystal/Downloads/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D4925C8B-7701-1C45-B167-940F89EBEB61}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{9AE7747B-EBA3-9B45-A684-C3773709611F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="760" windowWidth="34560" windowHeight="20680" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,8 +19,350 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>Krystal</author>
+  </authors>
+  <commentList>
+    <comment ref="P1" authorId="0" shapeId="0" xr:uid="{75B51053-D224-B649-8E99-981F3F432820}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft YaHei"/>
+            <family val="34"/>
+            <charset val="134"/>
+          </rPr>
+          <t>標籤：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft YaHei"/>
+            <family val="34"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft YaHei"/>
+            <family val="34"/>
+            <charset val="134"/>
+          </rPr>
+          <t>用</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft YaHei"/>
+            <family val="34"/>
+            <charset val="134"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft YaHei"/>
+            <family val="34"/>
+            <charset val="134"/>
+          </rPr>
+          <t>來區分</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="Q1" authorId="0" shapeId="0" xr:uid="{89DB849F-C242-1948-BE88-93B5BA1CA824}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>出貨星期：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>輸入</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>星期一</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>星期二</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>星期三</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>用</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="Microsoft JhengHei UI"/>
+            <family val="1"/>
+            <charset val="1"/>
+          </rPr>
+          <t>來區分</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="R1" authorId="0" shapeId="0" xr:uid="{A54ABBC2-2A4C-104F-A4FA-DE21325C91FB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>出貨星期：</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>輸入</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>桶裝水</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>雞蛋</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>飲水機</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t xml:space="preserve">
+</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>用</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>,</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="24"/>
+            <color rgb="FF000000"/>
+            <rFont val="新細明體"/>
+            <family val="1"/>
+            <charset val="136"/>
+            <scheme val="minor"/>
+          </rPr>
+          <t>來區分</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="33" uniqueCount="33">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="31" uniqueCount="31">
   <si>
     <t>客戶名稱</t>
   </si>
@@ -70,35 +412,10 @@
     <t>標籤</t>
   </si>
   <si>
-    <t>批發</t>
-  </si>
-  <si>
     <t>活躍</t>
   </si>
   <si>
     <t>個人</t>
-  </si>
-  <si>
-    <t>展覽</t>
-  </si>
-  <si>
-    <t>(03) 5555-0000</t>
-  </si>
-  <si>
-    <t>0988-000111</t>
-  </si>
-  <si>
-    <t>lin.xiao.jie@gmail.com</t>
-  </si>
-  <si>
-    <t>新竹市東區光復路20號</t>
-  </si>
-  <si>
-    <t>潛在大訂單客戶</t>
-  </si>
-  <si>
-    <t>難溝通</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>出貨星期</t>
@@ -109,21 +426,44 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>雞蛋</t>
-  </si>
-  <si>
-    <t>現金</t>
-  </si>
-  <si>
-    <t>吳先生</t>
+    <t>零售</t>
+  </si>
+  <si>
+    <t>預付</t>
+  </si>
+  <si>
+    <t>收付方式</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>星期一,星期二</t>
+    <t>張美美</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>收付方式</t>
+    <t>其他</t>
+  </si>
+  <si>
+    <t>04-12345678</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>meimei@gmail.com</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>台中市測試</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>標籤一,標籤二</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>星期一,星期四</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>雞蛋,飲水機</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -131,7 +471,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3">
+  <fonts count="10">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -147,11 +487,66 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="16"/>
-      <color theme="1"/>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="新細明體"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft JhengHei UI"/>
+      <family val="1"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="新細明體"/>
+      <family val="1"/>
+      <charset val="136"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="18"/>
+      <color theme="1"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="18"/>
+      <color theme="10"/>
+      <name val="Microsoft YaHei"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <color rgb="FF000000"/>
+      <name val="Microsoft YaHei"/>
+      <family val="34"/>
+      <charset val="134"/>
     </font>
   </fonts>
   <fills count="2">
@@ -171,15 +566,18 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="1" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="一般" xfId="0" builtinId="0"/>
+    <cellStyle name="超連結" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
@@ -478,23 +876,24 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:S2"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="22"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="17.59765625" defaultRowHeight="26"/>
   <cols>
-    <col min="1" max="1" width="18" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="5" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="21.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="33" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="21.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="46.19921875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="15.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.19921875" style="1" hidden="1" customWidth="1"/>
-    <col min="13" max="14" width="15.3984375" style="1" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="22.796875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="16.3984375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="21.3984375" style="1" customWidth="1"/>
-    <col min="20" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="43.19921875" style="1" customWidth="1"/>
+    <col min="2" max="5" width="19.59765625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="29.59765625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="48" style="1" customWidth="1"/>
+    <col min="9" max="9" width="29.59765625" style="1" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="64.3984375" style="1" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="29.59765625" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10" style="1" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="17.796875" style="1" hidden="1" customWidth="1"/>
+    <col min="14" max="14" width="18.59765625" style="1" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="41.796875" style="1" customWidth="1"/>
+    <col min="16" max="18" width="39.19921875" style="1" customWidth="1"/>
+    <col min="19" max="19" width="17.796875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="16384" width="17.59765625" style="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:19">
@@ -547,74 +946,59 @@
         <v>15</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>27</v>
+        <v>19</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
     </row>
     <row r="2" spans="1:19">
       <c r="A2" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>17</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="G2" s="1">
+        <v>912345678</v>
+      </c>
+      <c r="H2" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="R2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="B2" s="1" t="s">
-        <v>18</v>
-      </c>
-      <c r="C2" s="1" t="s">
-        <v>16</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>17</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>20</v>
-      </c>
-      <c r="G2" s="1" t="s">
+      <c r="S2" s="1" t="s">
         <v>21</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="J2" s="1" t="s">
-        <v>23</v>
-      </c>
-      <c r="M2" s="1">
-        <v>200000</v>
-      </c>
-      <c r="N2" s="1">
-        <v>45</v>
-      </c>
-      <c r="O2" s="1" t="s">
-        <v>24</v>
-      </c>
-      <c r="P2" s="1" t="s">
-        <v>25</v>
-      </c>
-      <c r="Q2" s="1" t="s">
-        <v>31</v>
-      </c>
-      <c r="R2" s="1" t="s">
-        <v>28</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
-  <dataValidations count="7">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="Q3:Q1048576" xr:uid="{49849252-71BC-1F4A-BEB5-286409FC4E1A}">
-      <formula1>"1,2,3,4,5,6,7"</formula1>
-    </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="R2 R3:R1048576" xr:uid="{DFE60689-5F5C-564B-BA41-84657FD32DA5}">
-      <formula1>"桶裝水,雞蛋,飲水機"</formula1>
-    </dataValidation>
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="E2:E1048576" xr:uid="{346D0CE5-9218-2E43-86CD-F31CF4DC0980}">
       <formula1>"活躍,潛在客戶"</formula1>
     </dataValidation>
@@ -631,6 +1015,10 @@
       <formula1>"現金,月結,預付"</formula1>
     </dataValidation>
   </dataValidations>
+  <hyperlinks>
+    <hyperlink ref="H2" r:id="rId1" xr:uid="{8130888C-66A7-B847-A165-45858A7352EA}"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>